--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -269,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -344,7 +344,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>単位コードUCUMにおける実投与日数の単位。dで固定される</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -402,7 +402,7 @@
 </t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -417,7 +417,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -835,7 +835,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -811,42 +811,42 @@
   <dimension ref="A1:AK13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.2109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.2109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="226.484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="194.171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.2890625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="68.94921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="59.11328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
